--- a/pettycash/templates/excel_templates/PCV_template.xlsx
+++ b/pettycash/templates/excel_templates/PCV_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rpalv\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\tesda_pcvms\pettycash\templates\excel_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7599605B-BD65-4E3C-8531-7AB996A12F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974CF4A5-910E-4059-9C5E-DBD6D1C50CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="39">
   <si>
     <t>Particulars</t>
   </si>
@@ -134,9 +134,6 @@
   </si>
   <si>
     <t>Cash Received:</t>
-  </si>
-  <si>
-    <t>ROEL A. DULDULAO</t>
   </si>
   <si>
     <t xml:space="preserve">Entity Name: </t>
@@ -532,7 +529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
@@ -622,10 +619,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -637,36 +661,10 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -936,12 +934,12 @@
       <c r="U1" s="1"/>
     </row>
     <row r="2" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
       <c r="E2" s="2"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -952,7 +950,7 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="4"/>
+      <c r="M2" s="3"/>
       <c r="N2" s="2"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -974,8 +972,8 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
       <c r="N3" s="6"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
@@ -987,11 +985,11 @@
     </row>
     <row r="4" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="1"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
       <c r="E4" s="6"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -1001,9 +999,9 @@
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="8"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="6"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
@@ -1017,8 +1015,8 @@
         <v>8</v>
       </c>
       <c r="B5" s="1"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
       <c r="E5" s="6"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -1088,8 +1086,8 @@
         <v>9</v>
       </c>
       <c r="B8" s="1"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
       <c r="E8" s="6"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -1115,8 +1113,8 @@
         <v>11</v>
       </c>
       <c r="B9" s="1"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
       <c r="E9" s="6"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -1186,11 +1184,11 @@
       <c r="U11" s="19"/>
     </row>
     <row r="12" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="56"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="47"/>
       <c r="D12" s="20" t="s">
         <v>1</v>
       </c>
@@ -1242,9 +1240,9 @@
     <row r="14" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="1"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="47"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="60"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
         <v>17</v>
@@ -1267,9 +1265,9 @@
     <row r="15" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="47"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="60"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
         <v>18</v>
@@ -1495,11 +1493,11 @@
     </row>
     <row r="24" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
-      <c r="B24" s="43" t="s">
+      <c r="B24" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="49"/>
-      <c r="D24" s="49"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
       <c r="E24" s="1"/>
       <c r="F24" s="5"/>
       <c r="G24" s="1"/>
@@ -1555,11 +1553,11 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="44"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="49"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="51"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="51"/>
+      <c r="L26" s="51"/>
+      <c r="M26" s="51"/>
+      <c r="N26" s="53"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
@@ -1578,11 +1576,11 @@
       <c r="G27" s="32"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="49"/>
-      <c r="L27" s="49"/>
-      <c r="M27" s="49"/>
-      <c r="N27" s="51"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="51"/>
+      <c r="L27" s="51"/>
+      <c r="M27" s="51"/>
+      <c r="N27" s="53"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
@@ -1603,13 +1601,13 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="44" t="s">
+      <c r="J28" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="K28" s="49"/>
-      <c r="L28" s="49"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="51"/>
+      <c r="K28" s="51"/>
+      <c r="L28" s="51"/>
+      <c r="M28" s="51"/>
+      <c r="N28" s="53"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
@@ -1630,13 +1628,13 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="44" t="s">
+      <c r="J29" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="K29" s="49"/>
-      <c r="L29" s="49"/>
-      <c r="M29" s="49"/>
-      <c r="N29" s="51"/>
+      <c r="K29" s="51"/>
+      <c r="L29" s="51"/>
+      <c r="M29" s="51"/>
+      <c r="N29" s="53"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
@@ -1682,11 +1680,11 @@
         <v>7</v>
       </c>
       <c r="I31" s="35"/>
-      <c r="J31" s="48"/>
-      <c r="K31" s="48"/>
-      <c r="L31" s="48"/>
-      <c r="M31" s="48"/>
-      <c r="N31" s="59"/>
+      <c r="J31" s="55"/>
+      <c r="K31" s="55"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="55"/>
+      <c r="N31" s="56"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
@@ -1898,9 +1896,7 @@
     <row r="40" spans="1:21" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
       <c r="B40" s="1"/>
-      <c r="C40" s="38" t="s">
-        <v>38</v>
-      </c>
+      <c r="C40" s="38"/>
       <c r="D40" s="1"/>
       <c r="E40" s="6"/>
       <c r="F40" s="1"/>
@@ -1930,11 +1926,11 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="49"/>
-      <c r="L41" s="49"/>
-      <c r="M41" s="49"/>
-      <c r="N41" s="51"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="51"/>
+      <c r="L41" s="51"/>
+      <c r="M41" s="51"/>
+      <c r="N41" s="53"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
@@ -1955,13 +1951,13 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="44" t="s">
+      <c r="J42" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="K42" s="49"/>
-      <c r="L42" s="49"/>
-      <c r="M42" s="49"/>
-      <c r="N42" s="51"/>
+      <c r="K42" s="51"/>
+      <c r="L42" s="51"/>
+      <c r="M42" s="51"/>
+      <c r="N42" s="53"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
@@ -1982,13 +1978,13 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
-      <c r="J43" s="44" t="s">
+      <c r="J43" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="K43" s="49"/>
-      <c r="L43" s="49"/>
-      <c r="M43" s="49"/>
-      <c r="N43" s="51"/>
+      <c r="K43" s="51"/>
+      <c r="L43" s="51"/>
+      <c r="M43" s="51"/>
+      <c r="N43" s="53"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
@@ -2025,20 +2021,20 @@
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="48"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="51"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="53"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I45" s="1"/>
-      <c r="J45" s="48"/>
-      <c r="K45" s="48"/>
-      <c r="L45" s="48"/>
-      <c r="M45" s="48"/>
-      <c r="N45" s="59"/>
+      <c r="J45" s="55"/>
+      <c r="K45" s="55"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="55"/>
+      <c r="N45" s="56"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
@@ -2117,12 +2113,12 @@
       <c r="U48" s="1"/>
     </row>
     <row r="49" spans="1:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="52" t="s">
+      <c r="A49" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="53"/>
-      <c r="C49" s="53"/>
-      <c r="D49" s="53"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="44"/>
+      <c r="D49" s="44"/>
       <c r="E49" s="2"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
@@ -2378,11 +2374,11 @@
       <c r="U58" s="1"/>
     </row>
     <row r="59" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="54" t="s">
+      <c r="A59" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B59" s="55"/>
-      <c r="C59" s="56"/>
+      <c r="B59" s="46"/>
+      <c r="C59" s="47"/>
       <c r="D59" s="20" t="s">
         <v>1</v>
       </c>
@@ -2435,7 +2431,7 @@
     <row r="61" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
       <c r="B61" s="1"/>
-      <c r="C61" s="57">
+      <c r="C61" s="61">
         <f t="shared" ref="C61" si="0">C14</f>
         <v>0</v>
       </c>
@@ -2469,7 +2465,7 @@
     <row r="62" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
       <c r="B62" s="1"/>
-      <c r="C62" s="58"/>
+      <c r="C62" s="49"/>
       <c r="D62" s="22"/>
       <c r="E62" s="23"/>
       <c r="F62" s="1"/>
@@ -2703,11 +2699,11 @@
     </row>
     <row r="71" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
-      <c r="B71" s="43" t="s">
+      <c r="B71" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="C71" s="49"/>
-      <c r="D71" s="49"/>
+      <c r="C71" s="51"/>
+      <c r="D71" s="51"/>
       <c r="E71" s="1"/>
       <c r="F71" s="5"/>
       <c r="G71" s="1"/>
@@ -2763,11 +2759,11 @@
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
-      <c r="J73" s="44"/>
-      <c r="K73" s="49"/>
-      <c r="L73" s="49"/>
-      <c r="M73" s="49"/>
-      <c r="N73" s="51"/>
+      <c r="J73" s="52"/>
+      <c r="K73" s="51"/>
+      <c r="L73" s="51"/>
+      <c r="M73" s="51"/>
+      <c r="N73" s="53"/>
       <c r="O73" s="1"/>
       <c r="P73" s="1"/>
       <c r="Q73" s="1"/>
@@ -2788,14 +2784,14 @@
       <c r="G74" s="32"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
-      <c r="J74" s="50">
+      <c r="J74" s="57">
         <f>C82</f>
         <v>0</v>
       </c>
-      <c r="K74" s="49"/>
-      <c r="L74" s="49"/>
-      <c r="M74" s="49"/>
-      <c r="N74" s="51"/>
+      <c r="K74" s="51"/>
+      <c r="L74" s="51"/>
+      <c r="M74" s="51"/>
+      <c r="N74" s="53"/>
       <c r="O74" s="1"/>
       <c r="P74" s="1"/>
       <c r="Q74" s="1"/>
@@ -2816,13 +2812,13 @@
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
-      <c r="J75" s="44" t="s">
+      <c r="J75" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="K75" s="49"/>
-      <c r="L75" s="49"/>
-      <c r="M75" s="49"/>
-      <c r="N75" s="51"/>
+      <c r="K75" s="51"/>
+      <c r="L75" s="51"/>
+      <c r="M75" s="51"/>
+      <c r="N75" s="53"/>
       <c r="O75" s="1"/>
       <c r="P75" s="1"/>
       <c r="Q75" s="1"/>
@@ -2843,13 +2839,13 @@
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
-      <c r="J76" s="44" t="s">
+      <c r="J76" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="K76" s="49"/>
-      <c r="L76" s="49"/>
-      <c r="M76" s="49"/>
-      <c r="N76" s="51"/>
+      <c r="K76" s="51"/>
+      <c r="L76" s="51"/>
+      <c r="M76" s="51"/>
+      <c r="N76" s="53"/>
       <c r="O76" s="1"/>
       <c r="P76" s="1"/>
       <c r="Q76" s="1"/>
@@ -2898,12 +2894,12 @@
         <v>7</v>
       </c>
       <c r="I78" s="35"/>
-      <c r="J78" s="48">
+      <c r="J78" s="55">
         <f>J92</f>
         <v>0</v>
       </c>
-      <c r="K78" s="49"/>
-      <c r="L78" s="49"/>
+      <c r="K78" s="51"/>
+      <c r="L78" s="51"/>
       <c r="M78" s="1"/>
       <c r="N78" s="6"/>
       <c r="O78" s="1"/>
@@ -3153,14 +3149,14 @@
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
-      <c r="J88" s="50">
+      <c r="J88" s="57">
         <f>C88</f>
         <v>0</v>
       </c>
-      <c r="K88" s="49"/>
-      <c r="L88" s="49"/>
-      <c r="M88" s="49"/>
-      <c r="N88" s="51"/>
+      <c r="K88" s="51"/>
+      <c r="L88" s="51"/>
+      <c r="M88" s="51"/>
+      <c r="N88" s="53"/>
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
@@ -3181,13 +3177,13 @@
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
-      <c r="J89" s="44" t="s">
+      <c r="J89" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="K89" s="49"/>
-      <c r="L89" s="49"/>
-      <c r="M89" s="49"/>
-      <c r="N89" s="51"/>
+      <c r="K89" s="51"/>
+      <c r="L89" s="51"/>
+      <c r="M89" s="51"/>
+      <c r="N89" s="53"/>
       <c r="O89" s="1"/>
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
@@ -3208,13 +3204,13 @@
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
-      <c r="J90" s="44" t="s">
+      <c r="J90" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="K90" s="49"/>
-      <c r="L90" s="49"/>
-      <c r="M90" s="49"/>
-      <c r="N90" s="51"/>
+      <c r="K90" s="51"/>
+      <c r="L90" s="51"/>
+      <c r="M90" s="51"/>
+      <c r="N90" s="53"/>
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
@@ -3251,24 +3247,24 @@
       <c r="B92" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C92" s="48">
+      <c r="C92" s="55">
         <f>C78</f>
         <v>0</v>
       </c>
-      <c r="D92" s="49"/>
-      <c r="E92" s="51"/>
+      <c r="D92" s="51"/>
+      <c r="E92" s="53"/>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
       <c r="H92" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I92" s="1"/>
-      <c r="J92" s="48">
+      <c r="J92" s="55">
         <f>C78</f>
         <v>0</v>
       </c>
-      <c r="K92" s="49"/>
-      <c r="L92" s="49"/>
+      <c r="K92" s="51"/>
+      <c r="L92" s="51"/>
       <c r="M92" s="39"/>
       <c r="N92" s="40"/>
       <c r="O92" s="1"/>
@@ -24142,27 +24138,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="J26:N26"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="J45:N45"/>
-    <mergeCell ref="J27:N27"/>
-    <mergeCell ref="J28:N28"/>
-    <mergeCell ref="J29:N29"/>
-    <mergeCell ref="J41:N41"/>
-    <mergeCell ref="J31:N31"/>
-    <mergeCell ref="J88:N88"/>
-    <mergeCell ref="J89:N89"/>
-    <mergeCell ref="J90:N90"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="J92:L92"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="D14:E15"/>
     <mergeCell ref="J78:L78"/>
     <mergeCell ref="J42:N42"/>
     <mergeCell ref="J43:N43"/>
@@ -24175,6 +24150,27 @@
     <mergeCell ref="J73:N73"/>
     <mergeCell ref="J74:N74"/>
     <mergeCell ref="J75:N75"/>
+    <mergeCell ref="J88:N88"/>
+    <mergeCell ref="J89:N89"/>
+    <mergeCell ref="J90:N90"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="J92:L92"/>
+    <mergeCell ref="J45:N45"/>
+    <mergeCell ref="J27:N27"/>
+    <mergeCell ref="J28:N28"/>
+    <mergeCell ref="J29:N29"/>
+    <mergeCell ref="J41:N41"/>
+    <mergeCell ref="J31:N31"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="J26:N26"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="D14:E15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
